--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.20959572509084</v>
+        <v>1.984059305327261</v>
       </c>
       <c r="D2" t="n">
-        <v>12.6325129776344</v>
+        <v>2.05278335886559</v>
       </c>
       <c r="E2" t="n">
-        <v>4.950609715254338</v>
+        <v>0.8044740787288298</v>
       </c>
       <c r="F2" t="n">
-        <v>3.549274858723405</v>
+        <v>0.5767571645425533</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.20985180736333</v>
+        <v>2.309100918696541</v>
       </c>
       <c r="D3" t="n">
-        <v>15.61946839442997</v>
+        <v>2.53816361409487</v>
       </c>
       <c r="E3" t="n">
-        <v>4.950609715254338</v>
+        <v>0.8044740787288298</v>
       </c>
       <c r="F3" t="n">
-        <v>3.549274858723405</v>
+        <v>0.5767571645425533</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.48676973393466</v>
+        <v>3.816600081764383</v>
       </c>
       <c r="D4" t="n">
-        <v>21.94648454711614</v>
+        <v>3.566303738906372</v>
       </c>
       <c r="E4" t="n">
-        <v>4.950609715254338</v>
+        <v>0.8044740787288298</v>
       </c>
       <c r="F4" t="n">
-        <v>3.549274858723405</v>
+        <v>0.5767571645425533</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.48027261627893</v>
+        <v>3.653044300145326</v>
       </c>
       <c r="D5" t="n">
-        <v>14.11110736720032</v>
+        <v>2.293054947170052</v>
       </c>
       <c r="E5" t="n">
-        <v>4.950609715254338</v>
+        <v>0.8044740787288298</v>
       </c>
       <c r="F5" t="n">
-        <v>3.549274858723405</v>
+        <v>0.5767571645425533</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
